--- a/testdata/config_platforme.xlsx
+++ b/testdata/config_platforme.xlsx
@@ -74,10 +74,10 @@
     <t>16</t>
   </si>
   <si>
-    <t>eu.newfrontier.iBanking.mobile.AIK.Retail.uat</t>
-  </si>
-  <si>
-    <t>eu.newfrontier.ibanking.mobile.aik.retail.ui.MainActivity</t>
+    <t>eu.newfrontier.iBanking.mobile.AIK.SBB.uat</t>
+  </si>
+  <si>
+    <t>com.nfinnova.legacy.MainActivity</t>
   </si>
   <si>
     <t>.</t>
